--- a/E/ALLFEST1.xlsx
+++ b/E/ALLFEST1.xlsx
@@ -19,7 +19,7 @@
     <t>10036619</t>
   </si>
   <si>
-    <t>MARJAN SRP LYCHE 460</t>
+    <t>MARJAN SRP LYCHE 425</t>
   </si>
   <si>
     <t>ALLFEST1</t>
@@ -37,7 +37,7 @@
     <t>20122092</t>
   </si>
   <si>
-    <t>MRJAN SYRP LEMON 460</t>
+    <t>MRJAN SYRP LEMON 425</t>
   </si>
 </sst>
 </file>
